--- a/data/output/evaluasi_72.xlsx
+++ b/data/output/evaluasi_72.xlsx
@@ -8,6 +8,19 @@
   </bookViews>
   <sheets>
     <sheet name="7200" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="7211" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="7271" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="7203" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="7207" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="7208" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7212" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7205" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="7201" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="7204" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="7206" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="7209" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="7210" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="7202" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,20 +484,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.10093496378721</v>
+        <v>33.53221931384181</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pkrt_q1-25 vs q-to-q_pkrt_q1-25.1</t>
+          <t>adhb_pi_q3-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -499,20 +512,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.842891289964244</v>
+        <v>29.31562767450389</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
+          <t>adhk_pi_q3-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -527,20 +540,4706 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-6.78814087389198</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q1-25 vs q-to-q_pdrb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
+      <c r="D5" t="n">
+        <v>-6.745695244593558</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>72</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-47.71661813236333</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q1-25 vs q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>34.54056680667226</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>72</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.944466376082714</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>72</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3578296124904425</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q2-25 vs q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>72</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8.927185348623864</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25 vs q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>72</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7.63070677320455</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>72</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6.784664734878364</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q2-25 vs y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>72</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.950485482156886</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>72</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-3.508819315119434</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>72</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-5.704056060233584</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>72</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3.008805125609269</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>72</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6.25415585667814</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q2-25 vs c-to-c_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>72</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5.491650330495919</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25 vs c-to-c_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>72</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-3.508819315119434</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>72</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-2.133535365598949</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25 vs implisit_q-to-q_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>72</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-1.842891289964244</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>72</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1.556137027416323</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q2-25 vs implisit_q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>72</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-2.114562989935265</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>72</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3.666666582505681</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q1-25 vs implisit_q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>72</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.392063025473853</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25 vs implisit_q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>72</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>4.220227372774009</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q2-25 vs implisit_y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>72</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2.773278454091026</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.052942836900328</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-8.173970222675239</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
       <c r="D4" t="n">
-        <v>-0.2415673968546127</v>
+        <v>3.738270212345403</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pdrb_q2-25 vs implisit_y-on-y_pdrb_q2-25.1</t>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-5.296500346563679</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6244168187110902</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8660241766518266</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.440640126001622</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.4300127041422501</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.05933428618586833</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-3.202940734965435</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.702309148523347</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6369010224677063</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.999057084765667</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8485401250617599</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.209376288972779</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.92909385034423</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8696296296296326</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-18.43545611015491</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.721387202212179</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3.942316470776082</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-14.8235111551329</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-5.727594459411344</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.277323558677194</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.7941688156132165</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7210</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Sigi</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.630406738260598</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7210</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sigi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.057513020293425</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7210</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sigi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5474292583126422</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7210</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sigi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.390800385075496</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7210</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sigi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.74336133400105</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7210</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sigi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6624708830356192</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.201917929719372</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.9250165969045524</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.850950855679199</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.047306904175989</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.04922950377614512</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-4.739672527289841</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.2251778690655607</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.431599412262962</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>45846.31</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>39303.74</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>adhb_pi_q2-25_ril vs adhb_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-41952.22999999998</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-45745.93000000005</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>adhb_net_ekspor_q2-25_ril vs adhb_net_ekspor_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-919.5299999999697</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-279.1199999999953</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q2-25_ril vs adhk_net_ekspor_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.7368979373818361</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.3778834349130231</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8352879785250821</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.7670173686709297</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6.200837454893851</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.531105389169448</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.009993938343918</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3.604201010955619</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.90120682841099</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-4.963392607264034</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-9.679430725657332</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-10.57975709387938</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>22260.56</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.1877182742632439</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q2-25_ril vs q-to-q_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.04596481607099003</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.1606482615376201</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q1-25_ril vs implisit_y-on-y_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.08778890626336897</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sog_q_pmtb_q2-25_ril vs sog_q_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.881886888747756</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.029700290574607</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3682100858308766</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.676247494564991</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4.046249306549397</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-9.812828927069269</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2779162817218965</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6.925933295906707</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4402890387740901</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q2-25_ril vs q-to-q_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.4505506094260417</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q2-25_ril vs implisit_q-to-q_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1808074484830073</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_q_pmtb_q2-25_ril vs sog_q_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.054919263715977</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.156921479662266</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.89160061332573</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.908306453375432</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-7.577403268358228</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.93651139438584</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9.204648589978568</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25_prov vs y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.8945824304050733</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.529856182750612</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.17203145605714</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.17203145605714</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.06600999851075229</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-4.129752665086253</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-10.57373420924391</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.149718960859386</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3.777327795629728</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.903087644916053</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.2761357221979041</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7.437115385291697</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3780074192837424</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q2-25_ril vs implisit_q-to-q_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.914609948927999</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.379286720392773</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.109366722142257</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.505613899738568</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.472000112614753</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7926870292327819</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-3.011192524303064</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.884541619705178</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-11.18845336359576</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.9746297319828</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.8342544329268</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.994437658295553</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.302996035225124</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>22.79497577377012</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>24.3660225324928</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9.010829145980743</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.09683358873293002</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7205</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Donggala</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.534688749949951</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7205</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Donggala</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.263262141500991</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7205</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Donggala</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-9.194067629712091</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7205</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Donggala</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>16.14256186395706</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7205</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Donggala</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0149082963789523</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7205</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Donggala</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7237981276564315</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7205</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Donggala</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.1324510515556238</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7205</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Donggala</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.433360665337942</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7201</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Kepulauan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.5045539701665664</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7201</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Kepulauan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8.539011315278188</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7201</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Kepulauan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6.732912568611218</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7201</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Kepulauan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.020849308802746</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7201</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Kepulauan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5245982020182629</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7201</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Kepulauan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.163796234038243</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_72.xlsx
+++ b/data/output/evaluasi_72.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
